--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -2064,13 +2064,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>29</v>
@@ -2079,22 +2079,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2114,42 +2117,51 @@
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -2169,7 +2181,7 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -2187,7 +2199,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -2198,8 +2210,17 @@
       <c r="P4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -2219,11 +2240,11 @@
         <v>90</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>95</v>
       </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
       <c r="I5">
         <v>100</v>
       </c>
@@ -2231,25 +2252,34 @@
         <v>100</v>
       </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>90</v>
       </c>
-      <c r="L5">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>95</v>
       </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2269,37 +2299,46 @@
         <v>85</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>95</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>96.7</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
         <v>93.3</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>85</v>
       </c>
-      <c r="L6">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>95</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>96.7</v>
       </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
-      <c r="O6">
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
         <v>93.3</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -2319,7 +2358,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -2337,7 +2376,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -2348,8 +2387,17 @@
       <c r="P7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -2369,37 +2417,46 @@
         <v>50</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>85</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>86.7</v>
       </c>
-      <c r="I8">
-        <v>100</v>
-      </c>
       <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
         <v>90</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>50</v>
       </c>
-      <c r="L8">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
         <v>85</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>86.7</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
         <v>90</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -2419,7 +2476,7 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -2437,7 +2494,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -2448,8 +2505,17 @@
       <c r="P9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2469,7 +2535,7 @@
         <v>90</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -2481,13 +2547,13 @@
         <v>100</v>
       </c>
       <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>90</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
       <c r="M10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -2496,10 +2562,19 @@
         <v>100</v>
       </c>
       <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>90</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2519,14 +2594,14 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
         <v>96.7</v>
       </c>
-      <c r="I11">
-        <v>100</v>
-      </c>
       <c r="J11">
         <v>100</v>
       </c>
@@ -2537,19 +2612,28 @@
         <v>100</v>
       </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
         <v>96.7</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
       <c r="P11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -2569,11 +2653,11 @@
         <v>100</v>
       </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>95</v>
       </c>
-      <c r="H12">
-        <v>100</v>
-      </c>
       <c r="I12">
         <v>100</v>
       </c>
@@ -2584,22 +2668,31 @@
         <v>100</v>
       </c>
       <c r="L12">
+        <v>100</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>95</v>
       </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -2619,37 +2712,46 @@
         <v>90</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
         <v>96.7</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>90</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>96.7</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -2669,37 +2771,46 @@
         <v>90</v>
       </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>95</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>90</v>
       </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>90</v>
       </c>
-      <c r="L14">
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>95</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>90</v>
       </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="S14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -2719,37 +2830,46 @@
         <v>50</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>75</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>90</v>
       </c>
-      <c r="I15">
-        <v>100</v>
-      </c>
       <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
         <v>93.3</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>50</v>
       </c>
-      <c r="L15">
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>75</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>90</v>
       </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
         <v>93.3</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -2769,37 +2889,46 @@
         <v>90</v>
       </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>95</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>96.7</v>
       </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>90</v>
       </c>
-      <c r="L16">
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>95</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>96.7</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>90</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -2819,37 +2948,46 @@
         <v>55</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>85</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>86.7</v>
       </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
       <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
         <v>90</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>55</v>
       </c>
-      <c r="L17">
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
         <v>85</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>86.7</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
+      <c r="P17">
+        <v>100</v>
+      </c>
+      <c r="Q17">
         <v>90</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -2869,37 +3007,46 @@
         <v>90</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
         <v>96.7</v>
       </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>90</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
         <v>96.7</v>
       </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -2919,37 +3066,46 @@
         <v>90</v>
       </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>95</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>93.3</v>
       </c>
-      <c r="I19">
-        <v>100</v>
-      </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>90</v>
       </c>
-      <c r="L19">
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>95</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>93.3</v>
       </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
       <c r="P19">
+        <v>100</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>90</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -2959,24 +3115,24 @@
       <c r="E20">
         <v>100</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>96.7</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
-      <c r="M20">
+      <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="O20">
         <v>96.7</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -143,15 +143,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -173,136 +173,61 @@
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CORONADO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>NATALIE</t>
   </si>
   <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
     <t>LIZBETH</t>
   </si>
   <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
     <t>GABRIELA DENISSE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>DANTE GAMALIEL</t>
@@ -810,25 +735,25 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -855,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -864,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -887,25 +812,25 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -938,10 +863,10 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -964,22 +889,22 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1006,10 +931,10 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1018,7 +943,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1041,25 +966,25 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1080,10 +1005,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1095,7 +1020,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1118,25 +1043,25 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1172,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1195,25 +1120,25 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1240,16 +1165,16 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1272,25 +1197,25 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1311,10 +1236,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1323,10 +1248,10 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1349,25 +1274,25 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1388,22 +1313,22 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1426,25 +1351,25 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1468,19 +1393,19 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1503,25 +1428,25 @@
         <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1542,13 +1467,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1557,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1580,25 +1505,25 @@
         <v>8</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1625,16 +1550,16 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1657,25 +1582,25 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1702,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1711,7 +1636,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1734,25 +1659,25 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1785,10 +1710,10 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1811,25 +1736,25 @@
         <v>5</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1865,7 +1790,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1888,25 +1813,25 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1939,10 +1864,10 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1965,25 +1890,25 @@
         <v>8</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2007,19 +1932,19 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2033,7 +1958,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2181,7 +2106,7 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -2199,7 +2124,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -2217,7 +2142,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2240,10 +2165,10 @@
         <v>90</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -2258,10 +2183,10 @@
         <v>90</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2276,7 +2201,7 @@
         <v>90</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2299,13 +2224,13 @@
         <v>85</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -2317,13 +2242,13 @@
         <v>85</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -2335,7 +2260,7 @@
         <v>85</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2358,7 +2283,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -2376,7 +2301,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -2394,7 +2319,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2417,13 +2342,13 @@
         <v>50</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I8">
-        <v>86.7</v>
+        <v>68.3</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -2432,16 +2357,16 @@
         <v>90</v>
       </c>
       <c r="L8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="O8">
-        <v>86.7</v>
+        <v>68.3</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -2450,10 +2375,10 @@
         <v>90</v>
       </c>
       <c r="R8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2476,7 +2401,7 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -2491,10 +2416,10 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -2509,10 +2434,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2535,10 +2460,10 @@
         <v>90</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -2550,13 +2475,13 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -2568,10 +2493,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2594,13 +2519,13 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I11">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -2609,16 +2534,16 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O11">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2627,10 +2552,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2653,10 +2578,10 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -2671,10 +2596,10 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -2689,7 +2614,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2712,10 +2637,10 @@
         <v>90</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I13">
         <v>96.7</v>
@@ -2730,10 +2655,10 @@
         <v>90</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O13">
         <v>96.7</v>
@@ -2748,7 +2673,7 @@
         <v>90</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2771,13 +2696,13 @@
         <v>90</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="I14">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -2789,13 +2714,13 @@
         <v>90</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="O14">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -2807,7 +2732,7 @@
         <v>90</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2830,13 +2755,13 @@
         <v>50</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="I15">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -2845,16 +2770,16 @@
         <v>93.3</v>
       </c>
       <c r="L15">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="O15">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2863,10 +2788,10 @@
         <v>93.3</v>
       </c>
       <c r="R15">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2889,10 +2814,10 @@
         <v>90</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I16">
         <v>96.7</v>
@@ -2907,10 +2832,10 @@
         <v>90</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O16">
         <v>96.7</v>
@@ -2925,7 +2850,7 @@
         <v>90</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2948,13 +2873,13 @@
         <v>55</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I17">
-        <v>86.7</v>
+        <v>68.3</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -2963,16 +2888,16 @@
         <v>90</v>
       </c>
       <c r="L17">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="O17">
-        <v>86.7</v>
+        <v>68.3</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -2981,10 +2906,10 @@
         <v>90</v>
       </c>
       <c r="R17">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3007,13 +2932,13 @@
         <v>90</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I18">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -3022,16 +2947,16 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O18">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -3040,10 +2965,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3066,13 +2991,13 @@
         <v>90</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -3081,16 +3006,16 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -3099,10 +3024,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3116,13 +3041,13 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="O20">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -3182,7 +3107,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>41</v>
@@ -3191,27 +3116,30 @@
         <v>16</v>
       </c>
       <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>56.2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>43.8</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
@@ -3220,19 +3148,19 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3243,7 +3171,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
@@ -3252,19 +3180,19 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>81.2</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3296,7 +3224,7 @@
         <v>17.6</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3376,7 +3304,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3403,323 +3331,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920111</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920116</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920117</v>
-      </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920118</v>
-      </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920266</v>
-      </c>
-      <c r="B7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920120</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920122</v>
-      </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920123</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920125</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920126</v>
-      </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920129</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920130</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920131</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920132</v>
-      </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3727,7 +3338,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3765,16 +3376,16 @@
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3788,39 +3399,39 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920118</v>
+        <v>21330051920125</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3828,45 +3439,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920118</v>
+        <v>21330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920121</v>
+        <v>21330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3874,45 +3485,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920121</v>
+        <v>21330051920126</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920123</v>
+        <v>21330051920120</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3923,42 +3534,42 @@
         <v>21330051920123</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>41</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920126</v>
+        <v>21330051920132</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3966,251 +3577,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920126</v>
+        <v>19330051920241</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920114</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920116</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920266</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920120</v>
-      </c>
-      <c r="B15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920122</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920125</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920129</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920131</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920132</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920241</v>
-      </c>
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -747,7 +747,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -824,7 +824,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -901,7 +901,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -978,7 +978,7 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1209,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1286,7 +1286,7 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1322,7 +1322,7 @@
         <v>5</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1363,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1440,7 +1440,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1517,7 +1517,7 @@
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>3</v>
@@ -1553,7 +1553,7 @@
         <v>6</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1594,7 +1594,7 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>3</v>
@@ -1630,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1671,7 +1671,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>3</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>3</v>
@@ -1825,7 +1825,7 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>8</v>
@@ -1902,7 +1902,7 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>3</v>
@@ -1961,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2236,7 +2236,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="L6">
         <v>85</v>
@@ -2254,7 +2254,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="R6">
         <v>85</v>
@@ -2354,7 +2354,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="L8">
         <v>25</v>
@@ -2372,7 +2372,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="R8">
         <v>25</v>
@@ -2708,7 +2708,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L14">
         <v>90</v>
@@ -2726,7 +2726,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R14">
         <v>90</v>
@@ -2767,7 +2767,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="L15">
         <v>65</v>
@@ -2785,7 +2785,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="R15">
         <v>65</v>
@@ -2885,7 +2885,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="L17">
         <v>52.5</v>
@@ -2903,7 +2903,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="R17">
         <v>52.5</v>
@@ -2944,7 +2944,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L18">
         <v>87.5</v>
@@ -2962,7 +2962,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R18">
         <v>87.5</v>
@@ -3044,13 +3044,13 @@
         <v>91.7</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O20">
         <v>91.7</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
   </sheetData>
@@ -3288,7 +3288,7 @@
         <v>11.8</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -179,6 +179,9 @@
     <t>MARIN</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -219,6 +225,9 @@
   </si>
   <si>
     <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>NATALIE</t>
@@ -907,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -943,7 +952,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -2242,7 +2251,7 @@
         <v>85</v>
       </c>
       <c r="M6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>90</v>
@@ -2260,7 +2269,7 @@
         <v>85</v>
       </c>
       <c r="S6">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3148,16 +3157,16 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>31.2</v>
       </c>
       <c r="H3">
         <v>7.3</v>
@@ -3338,7 +3347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3376,10 +3385,10 @@
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -3399,10 +3408,10 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3422,10 +3431,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -3445,10 +3454,10 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3468,10 +3477,10 @@
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -3491,10 +3500,10 @@
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3508,22 +3517,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920120</v>
+        <v>21330051920114</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3531,22 +3540,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920123</v>
+        <v>21330051920120</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3554,16 +3563,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920132</v>
+        <v>21330051920123</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -3577,24 +3586,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920241</v>
+        <v>21330051920132</v>
       </c>
       <c r="B11" t="s">
         <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920241</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
         <v>44</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
   <si>
     <t>Materia</t>
   </si>
@@ -143,18 +143,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
+    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -170,76 +170,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
     <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
-  </si>
-  <si>
-    <t>DANTE GAMALIEL</t>
   </si>
 </sst>
 </file>
@@ -765,28 +702,28 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -842,37 +779,37 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -919,22 +856,22 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -946,13 +883,13 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -996,28 +933,28 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1073,22 +1010,22 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1150,28 +1087,28 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1180,7 +1117,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1227,25 +1164,25 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1304,37 +1241,37 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>7</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>8</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1381,25 +1318,25 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1411,7 +1348,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1458,22 +1395,22 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1535,28 +1472,28 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1565,10 +1502,10 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1612,31 +1549,31 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1689,37 +1626,37 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>9</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1766,22 +1703,22 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1843,28 +1780,28 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>9</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -1920,37 +1857,37 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -1973,13 +1910,13 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2195,10 +2132,10 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -2207,7 +2144,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -2254,19 +2191,19 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O6">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>91.7</v>
+        <v>92.7</v>
       </c>
       <c r="R6">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -2372,22 +2309,22 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="O8">
-        <v>68.3</v>
+        <v>42.7</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q8">
-        <v>86.7</v>
+        <v>55.2</v>
       </c>
       <c r="R8">
-        <v>25</v>
+        <v>15.6</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2443,7 +2380,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -2490,7 +2427,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -2502,7 +2439,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -2549,19 +2486,19 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R11">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -2608,7 +2545,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -2667,19 +2604,19 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="O13">
-        <v>96.7</v>
+        <v>88.5</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R13">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -2726,19 +2663,19 @@
         <v>100</v>
       </c>
       <c r="N14">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="O14">
+        <v>88.5</v>
+      </c>
+      <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R14">
         <v>87.5</v>
-      </c>
-      <c r="O14">
-        <v>86.7</v>
-      </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
-      <c r="Q14">
-        <v>96.7</v>
-      </c>
-      <c r="R14">
-        <v>90</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -2785,22 +2722,22 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O15">
-        <v>91.7</v>
+        <v>74</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="R15">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2844,10 +2781,10 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O16">
-        <v>96.7</v>
+        <v>94.8</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -2856,10 +2793,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2903,22 +2840,22 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="O17">
-        <v>68.3</v>
+        <v>42.7</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q17">
-        <v>86.7</v>
+        <v>55.2</v>
       </c>
       <c r="R17">
-        <v>52.5</v>
+        <v>32.8</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2962,19 +2899,19 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O18">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R18">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3021,19 +2958,19 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O19">
-        <v>96.7</v>
+        <v>94.8</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R19">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3056,10 +2993,10 @@
         <v>96.7</v>
       </c>
       <c r="O20">
-        <v>91.7</v>
+        <v>93.8</v>
       </c>
       <c r="Q20">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3116,7 +3053,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>41</v>
@@ -3125,19 +3062,19 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>56.2</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2">
-        <v>43.8</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3148,7 +3085,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
@@ -3157,19 +3094,19 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>68.8</v>
+        <v>81.2</v>
       </c>
       <c r="G3" s="2">
-        <v>31.2</v>
+        <v>18.8</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3180,28 +3117,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>17.6</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3212,28 +3149,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>14</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>82.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="G5" s="2">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3244,7 +3181,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -3265,7 +3202,7 @@
         <v>12.5</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3347,7 +3284,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3379,254 +3316,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>21330051920125</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920125</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920125</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920126</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920120</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920123</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920132</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920241</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="56">
   <si>
     <t>Materia</t>
   </si>
@@ -170,10 +170,19 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>ZABDIEL</t>
@@ -1570,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -2725,7 +2734,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="O15">
-        <v>74</v>
+        <v>94.8</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3117,28 +3126,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>14</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>82.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="G4" s="2">
-        <v>17.6</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3149,10 +3158,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -3170,7 +3179,7 @@
         <v>12.5</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3181,28 +3190,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>87.5</v>
+        <v>88.2</v>
       </c>
       <c r="G6" s="2">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3284,7 +3293,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3316,24 +3325,70 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920126</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920125</v>
+      </c>
+      <c r="B4" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
         <v>41</v>
       </c>
-      <c r="G2">
+      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -732,10 +732,10 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -806,22 +806,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -883,22 +883,22 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -960,13 +960,13 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1114,22 +1114,22 @@
         <v>8</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1268,22 +1268,22 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1345,19 +1345,19 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1422,22 +1422,22 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1499,22 +1499,22 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1576,16 +1576,16 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1653,19 +1653,19 @@
         <v>5</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1807,22 +1807,22 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1884,22 +1884,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1925,10 +1925,10 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3083,7 +3083,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>18.8</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>12.5</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>11.8</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>11.8</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5APV - Estadisticos 20231.xlsx
+++ b/grupos/5APV - Estadisticos 20231.xlsx
@@ -732,10 +732,10 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -806,22 +806,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -883,22 +883,22 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -960,13 +960,13 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1114,22 +1114,22 @@
         <v>8</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1191,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1268,22 +1268,22 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1345,19 +1345,19 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1422,22 +1422,22 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1499,22 +1499,22 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1576,16 +1576,16 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1653,19 +1653,19 @@
         <v>5</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1807,22 +1807,22 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1884,22 +1884,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1925,10 +1925,10 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3083,7 +3083,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>18.8</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>12.5</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>12.5</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>11.8</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>11.8</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
